--- a/SGC-CKN/Excel/e915476e-8437-472a-ad47-69c69a342c0c_Lô_CT-02_P7_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/e915476e-8437-472a-ad47-69c69a342c0c_Lô_CT-02_P7_D800_26-03-2026.xlsx
@@ -1203,7 +1203,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.2</v>
@@ -1212,10 +1212,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="J11" s="8">
-        <v>7.4</v>
+        <v>14.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1685,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.2</v>
@@ -1694,10 +1694,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="I2" s="8">
-        <v>7.4</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1975,7 +1975,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.57</v>
@@ -1984,10 +1984,10 @@
         <v>6.8</v>
       </c>
       <c r="H12" s="39">
-        <v>41.07</v>
+        <v>44.57</v>
       </c>
       <c r="I12" s="39">
-        <v>6.04</v>
+        <v>6.55</v>
       </c>
     </row>
   </sheetData>
